--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -34,14 +34,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_ヘルプ先交通費'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_設定変更履歴'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_月次給与実績'!$A$1:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_日次給与実績'!$A$1:$M$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_日次給与実績'!$A$1:$M$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_インポートCSV_KingOfTime_sample'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_インポートCSV_ジョブカン_sample'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_インポートCSV_異常系_sample'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_インポートCSV_給与設定_sample'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11_インポートCSV_先頭説明行あり_sample'!$A$1:$A$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'12_従業員マスタ_設定未入力'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'13_勤務データ_2026-05_全稼働日'!$A$1:$K$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'13_勤務データ_2026-05_全稼働日'!$A$1:$K$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'14_勤務データ_2026-06_月中改定検証'!$A$1:$K$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'15_移行前後_突合テンプレート'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'16_前回取込_設定_差分確認用'!$A$1:$F$6</definedName>
@@ -618,7 +618,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>月次給与実績（確定した算式で再作成）</t>
+          <t>月次給与実績（確定した算式で再作成・5名）</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>日次給与実績</t>
+          <t>日次給与実績（5名・日次人件費合計＝月次）</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2026-05の全稼働日（月次と1円まで一致）</t>
+          <t>2026-05の全稼働日（5名・月次と1円まで一致）</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2958,12 +2958,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -2973,17 +2973,17 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -3015,12 +3015,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3030,17 +3030,17 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -3072,12 +3072,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -3186,12 +3186,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -3201,17 +3201,17 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -3243,32 +3243,32 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -3300,32 +3300,32 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -3357,32 +3357,32 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -3414,32 +3414,32 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -3471,32 +3471,32 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -3528,32 +3528,32 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -3585,32 +3585,32 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -3642,17 +3642,17 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -3677,17 +3677,17 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -3699,17 +3699,17 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -3734,17 +3734,17 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -3756,42 +3756,42 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -3813,32 +3813,32 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -3863,39 +3863,39 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -3927,32 +3927,32 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -3984,32 +3984,32 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -4041,17 +4041,17 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -4076,54 +4076,54 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -4155,32 +4155,32 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -4212,32 +4212,32 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -4269,32 +4269,32 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -4326,32 +4326,32 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -4361,54 +4361,54 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -4440,32 +4440,32 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -4497,32 +4497,32 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -4554,32 +4554,32 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -4611,32 +4611,32 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -4651,49 +4651,49 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
@@ -4725,32 +4725,32 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -4782,32 +4782,32 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
@@ -4839,62 +4839,2399 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>EMP-005</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>渡辺 由美</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K55" s="6" t="inlineStr">
+      <c r="K75" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K55"/>
+  <autoFilter ref="A1:K96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10916,7 +13253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12344,12 +14681,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -12359,17 +14696,17 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -12399,24 +14736,24 @@
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -12426,17 +14763,17 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -12466,24 +14803,24 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -12493,17 +14830,17 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -12533,24 +14870,24 @@
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -12560,17 +14897,17 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -12600,24 +14937,24 @@
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -12627,17 +14964,17 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -12667,44 +15004,44 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -12734,44 +15071,44 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -12801,44 +15138,44 @@
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -12868,44 +15205,44 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -12935,44 +15272,44 @@
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -13002,44 +15339,44 @@
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -13069,44 +15406,44 @@
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -13136,29 +15473,29 @@
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -13173,7 +15510,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -13183,17 +15520,17 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -13203,29 +15540,29 @@
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -13240,7 +15577,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -13250,17 +15587,17 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -13270,54 +15607,54 @@
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>EMP-003</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -13337,44 +15674,44 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -13384,7 +15721,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -13399,12 +15736,12 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -13416,32 +15753,32 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -13451,7 +15788,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -13471,7 +15808,7 @@
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -13483,32 +15820,32 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -13518,7 +15855,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -13538,7 +15875,7 @@
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -13550,32 +15887,32 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -13585,7 +15922,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -13605,7 +15942,7 @@
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -13617,17 +15954,17 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-002</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>佐藤 花子</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -13637,12 +15974,12 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -13652,64 +15989,64 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -13719,7 +16056,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -13739,44 +16076,44 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -13786,7 +16123,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -13806,44 +16143,44 @@
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -13853,7 +16190,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -13873,44 +16210,44 @@
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -13920,7 +16257,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -13940,44 +16277,44 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -13987,64 +16324,64 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -14054,7 +16391,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -14074,44 +16411,44 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -14121,7 +16458,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -14141,44 +16478,44 @@
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -14188,7 +16525,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -14208,44 +16545,44 @@
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -14255,7 +16592,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -14275,44 +16612,44 @@
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -14327,59 +16664,59 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -14389,7 +16726,7 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
@@ -14409,44 +16746,44 @@
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -14456,7 +16793,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -14476,44 +16813,44 @@
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>EMP-005</t>
+          <t>EMP-003</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>渡辺 由美</t>
+          <t>鈴木 一郎</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -14528,12 +16865,12 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
@@ -14543,84 +16880,2831 @@
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>650</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>EMP-005</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>渡辺 由美</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>16554</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>渡辺 由美</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K55" s="6" t="inlineStr">
+      <c r="K75" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr">
+      <c r="L75" s="6" t="inlineStr">
         <is>
           <t>14477</t>
         </is>
       </c>
-      <c r="M55" s="6" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
         <is>
           <t>750</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>14822</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>EMP-007</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>山本 大輔</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>14821</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:M96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">

--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -12013,7 +12013,9 @@
       <c r="J6" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="L6" s="4" t="n">
         <v>120</v>
       </c>
@@ -12064,7 +12066,9 @@
       <c r="J7" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="L7" s="4" t="n">
         <v>80</v>
       </c>
@@ -12170,7 +12174,9 @@
       <c r="J9" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="L9" s="4" t="n">
         <v>120</v>
       </c>
@@ -12276,7 +12282,9 @@
       <c r="J11" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="L11" s="4" t="n">
         <v>80</v>
       </c>
@@ -12382,7 +12390,9 @@
       <c r="J13" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="L13" s="4" t="n">
         <v>120</v>
       </c>
@@ -12488,7 +12498,9 @@
       <c r="J15" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="L15" s="4" t="n">
         <v>60</v>
       </c>
@@ -13340,7 +13352,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>320000</v>
+        <v>338000</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>20</v>
@@ -13378,7 +13390,7 @@
         <v>357600</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>37600</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="5">
@@ -13408,7 +13420,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>280000</v>
+        <v>295000</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>20</v>
@@ -13446,7 +13458,7 @@
         <v>300250</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>20250</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="6">
@@ -13476,9 +13488,11 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>144000</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+        <v>153000</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="H6" s="4" t="n">
         <v>120</v>
       </c>
@@ -13514,7 +13528,7 @@
         <v>154300</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>10300</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="7">
@@ -13544,7 +13558,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>350000</v>
+        <v>372000</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>20</v>
@@ -13582,7 +13596,7 @@
         <v>407912</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>57912</v>
+        <v>35912</v>
       </c>
     </row>
     <row r="8">
@@ -13612,7 +13626,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>300000</v>
+        <v>330000</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>20</v>
@@ -13650,7 +13664,7 @@
         <v>341250</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>41250</v>
+        <v>11250</v>
       </c>
     </row>
   </sheetData>

--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -12174,9 +12174,7 @@
       <c r="J9" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v>15</v>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="n">
         <v>120</v>
       </c>
@@ -12390,9 +12388,7 @@
       <c r="J13" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>15</v>
-      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="n">
         <v>120</v>
       </c>

--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -594,11 +594,11 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>S-05 T-D11</t>
+          <t>S-05 T-D11 T-D12</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="117" customHeight="1">

--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -548,11 +548,11 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>S-04 T-L01 T-L08 T-L06 T-R02 T-R04 T-R07 T-R10 T-D01 T-D04 T-D06 T-D08 T-E04 T-E07 T-E08 T-N02 T-Z05 C-000 C-018</t>
+          <t>S-04 T-L01 T-L08 T-L06 T-R02 T-R04 T-R07 T-R10 T-D01 T-D04 T-D06 T-D08 T-D13 T-E04 T-E07 T-E08 T-N02 T-Z05 C-000 C-018</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -601,7 +601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="117" customHeight="1">
+    <row r="9" ht="130" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>05_月次給与実績.tsv</t>
@@ -617,11 +617,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>S-03 S-05 S-08 T-L08 T-L10 T-D01 T-D04 T-D09 T-P01 T-P02 T-H01 T-H02 T-H04 T-A02 T-A09 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-001 C-003 C-005 C-011 C-018 C-019 C-013 C-017 C-008</t>
+          <t>S-03 S-05 S-08 T-L08 T-L10 T-D01 T-D04 T-D09 T-P01 T-P02 T-D13 T-H01 T-H02 T-H04 T-A02 T-A09 T-A10 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-001 C-003 C-005 C-011 C-018 C-019 C-013 C-017 C-008</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="104" customHeight="1">
@@ -640,11 +640,11 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>S-03 S-05 S-08 T-L08 T-D01 T-D04 T-D09 T-P01 T-H01 T-H02 T-H04 T-A02 T-A09 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-000 C-003 C-018 C-019 C-013 C-017</t>
+          <t>S-03 S-05 S-08 T-L08 T-D01 T-D04 T-D09 T-P01 T-H01 T-H02 T-H04 T-A02 T-A09 T-A10 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-000 C-003 C-018 C-019 C-013 C-017</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -778,11 +778,11 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>S-06</t>
+          <t>S-06 T-A10</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -11768,7 +11768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11784,6 +11784,7 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11821,40 +11822,45 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>在籍状態</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>給与単位</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>単位給与額</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>交通費単位</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>単位交通費</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>想定労働日数</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>所定労働時間</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>みなし残業時間</t>
         </is>
@@ -11888,30 +11894,35 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>320000</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>18000</v>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -11939,30 +11950,35 @@
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>280000</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -11994,32 +12010,37 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>パート</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>時給</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>日額</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12047,32 +12068,37 @@
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
           <t>アルバイト</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>時給</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>1100</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>日額</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12104,30 +12130,35 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>350000</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>22000</v>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -12155,30 +12186,35 @@
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
           <t>パート</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>時給</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>日額</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12206,30 +12242,35 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -12261,32 +12302,37 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
           <t>アルバイト</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>時給</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>1050</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>日額</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12318,30 +12364,35 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>260000</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>16000</v>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -12369,30 +12420,35 @@
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
           <t>パート</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>時給</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>1250</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>日額</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12424,30 +12480,35 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>410000</v>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>19000</v>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12475,32 +12536,37 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
           <t>アルバイト</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>時給</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="4" t="n">
-        <v>60</v>
-      </c>
       <c r="M15" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="N15" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -532,7 +532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="78" customHeight="1">
+    <row r="6" ht="91" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>02_従業員マスタ.tsv</t>
@@ -548,11 +548,11 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>S-04 T-L01 T-L08 T-L06 T-R02 T-R04 T-R07 T-R10 T-D01 T-D04 T-D06 T-D08 T-D13 T-E04 T-E07 T-E08 T-N02 T-Z05 C-000 C-018</t>
+          <t>S-04 T-L01 T-L08 T-L06 T-R02 T-R04 T-R07 T-R10 T-D01 T-D04 T-D06 T-D08 T-D13 T-D14 T-E04 T-E07 T-E08 T-N02 T-Z05 C-000 C-021 C-018</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -578,7 +578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="14" customHeight="1">
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>04_設定変更履歴.tsv</t>
@@ -594,14 +594,14 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>S-05 T-D11 T-D12</t>
+          <t>S-05 T-D11 T-D12 T-D14</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" ht="130" customHeight="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="143" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>05_月次給与実績.tsv</t>
@@ -617,11 +617,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>S-03 S-05 S-08 T-L08 T-L10 T-D01 T-D04 T-D09 T-P01 T-P02 T-D13 T-H01 T-H02 T-H04 T-A02 T-A09 T-A10 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-001 C-003 C-005 C-011 C-018 C-019 C-013 C-017 C-008</t>
+          <t>S-03 S-05 S-08 T-L08 T-L10 T-D01 T-D04 T-D09 T-P01 T-P02 T-D13 T-D14 T-H01 T-H02 T-H04 T-A02 T-A09 T-A10 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-001 C-003 C-005 C-011 C-018 C-020 C-019 C-013 C-017 C-008</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="104" customHeight="1">
@@ -640,11 +640,11 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>S-03 S-05 S-08 T-L08 T-D01 T-D04 T-D09 T-P01 T-H01 T-H02 T-H04 T-A02 T-A09 T-A10 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-000 C-003 C-018 C-019 C-013 C-017</t>
+          <t>S-03 S-05 S-08 T-L08 T-D01 T-D04 T-D09 T-P01 T-H01 T-H02 T-H04 T-A02 T-A09 T-A10 T-A05 T-A07 T-A08 T-E09 T-N03 T-Z05 C-000 C-003 C-018 C-020 C-019 C-013 C-017</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -808,7 +808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="14" customHeight="1">
+    <row r="18" ht="26" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>14_勤務データ_2026-06_月中改定検証.tsv</t>
@@ -824,11 +824,11 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>S-07 C-006 C-011</t>
+          <t>S-07 C-006 C-021 C-011 C-020</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">

--- a/20260805_従業員管理_04_検証データセット.xlsx
+++ b/20260805_従業員管理_04_検証データセット.xlsx
@@ -663,11 +663,11 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>S-06 T-I03 T-I17 T-I20</t>
+          <t>S-06 T-I03 T-I17 T-I20 T-I21</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -962,11 +962,11 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>S-04 T-I20</t>
+          <t>S-04 T-I20 T-I21</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
